--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="498">
   <si>
     <t>Filename</t>
   </si>
@@ -808,685 +808,706 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9818,0.0014,0.0105,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9942,0.0013,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.0080,0.0007,0.0002,0.9969</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9856,0.0010,0.0061,0.0013</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.9703,0.0010,0.0000,0.0114</t>
+  </si>
+  <si>
+    <t>0.0309,0.0000,0.0000,0.9934</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0020,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0027,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0019,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0440,0.0012,0.9617,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0006,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.7578,0.0004,0.3949,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.9916,0.0012,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0028,0.0000</t>
+  </si>
+  <si>
+    <t>0.5938,0.5156,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7247,0.0007,0.3065,0.0007</t>
+  </si>
+  <si>
+    <t>0.9600,0.0011,0.0293,0.0002</t>
+  </si>
+  <si>
+    <t>0.0029,0.0009,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0015,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0197,0.0005,0.9848,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9992,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9998,0.0010</t>
+  </si>
+  <si>
+    <t>0.1216,0.8679,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.9809,0.0168,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9985,0.0013</t>
+  </si>
+  <si>
+    <t>0.0100,0.3480,0.6158,0.0001</t>
+  </si>
+  <si>
+    <t>0.9702,0.0255,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.0100,0.0522,0.9863,0.0040</t>
+  </si>
+  <si>
+    <t>0.0098,0.9865,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.0027,0.9926,0.0102,0.0003</t>
+  </si>
+  <si>
+    <t>0.0064,0.5418,0.7757,0.0014</t>
+  </si>
+  <si>
+    <t>0.0005,0.0010,0.9980,0.0007</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.1414,0.0006,0.8732,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0018,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.9864,0.0168,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9352,0.0004,0.8982</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.3846,0.9878,0.0000</t>
+  </si>
+  <si>
+    <t>0.0086,0.0010,0.9898,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0055,0.0002,0.9964,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9948,0.0034,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9953,0.0022,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0028,0.9992,0.0003</t>
+  </si>
+  <si>
+    <t>0.9935,0.0032,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9948,0.0047,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.8934,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0004,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9961,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9985,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9279,0.0039,0.0704,0.0001</t>
+  </si>
+  <si>
+    <t>0.9843,0.0123,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0018,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.7286,0.9459,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.7750,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9663,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0049,0.9994</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0136,0.0000,0.0000,0.9978</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0012,0.9998</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0004,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.5893,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.8654,0.9795,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.8226,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.9285,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0027,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0032,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0031,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0024,0.0001,0.0000</t>
+  </si>
+  <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9989,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0027,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0333,0.0253,0.9178,0.0006</t>
-  </si>
-  <si>
-    <t>0.0016,0.0011,0.9977,0.0003</t>
-  </si>
-  <si>
-    <t>0.9478,0.0010,0.0567,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0004,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0001,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0022,0.0000</t>
-  </si>
-  <si>
-    <t>0.0177,0.9815,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9371,0.0001,0.0718,0.0001</t>
-  </si>
-  <si>
-    <t>0.0387,0.0019,0.9407,0.0020</t>
-  </si>
-  <si>
-    <t>0.0010,0.0015,0.9976,0.0002</t>
-  </si>
-  <si>
-    <t>0.0272,0.0098,0.9223,0.0039</t>
-  </si>
-  <si>
-    <t>0.2131,0.0006,0.8620,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9987,0.0014</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.1390,0.8459,0.0040,0.0003</t>
-  </si>
-  <si>
-    <t>0.5552,0.3719,0.0182,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9998,0.0035</t>
-  </si>
-  <si>
-    <t>0.0023,0.9906,0.0094,0.0000</t>
-  </si>
-  <si>
-    <t>0.9325,0.0504,0.0063,0.0022</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0348,0.9731,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0190,0.9645,0.0269,0.0011</t>
-  </si>
-  <si>
-    <t>0.0128,0.2996,0.6059,0.0049</t>
-  </si>
-  <si>
-    <t>0.0007,0.0012,0.9971,0.0006</t>
-  </si>
-  <si>
-    <t>0.0035,0.0032,0.9907,0.0007</t>
-  </si>
-  <si>
-    <t>0.0030,0.0001,0.9962,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0021,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.9920,0.0059,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0005,0.9981,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.9664,0.0011,0.8250</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0385,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.0011,0.9953,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0128,0.9977,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9925,0.0068,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.0026,0.9989,0.0005</t>
-  </si>
-  <si>
-    <t>0.9966,0.0017,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9958,0.0027,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9926,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9997,0.0000</t>
+    <t>0.9946,0.0099,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0004,0.9993,0.0009,0.0000</t>
+    <t>0.0014,0.0011,0.9978,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0049,0.0001,0.9947,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0020,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9976,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.2326,0.7698,0.0043,0.0001</t>
+  </si>
+  <si>
+    <t>0.4115,0.0060,0.5150,0.0011</t>
+  </si>
+  <si>
+    <t>0.2024,0.0002,0.8760,0.0001</t>
+  </si>
+  <si>
+    <t>0.2068,0.0641,0.4031,0.0023</t>
+  </si>
+  <si>
+    <t>0.4273,0.0026,0.5251,0.0030</t>
+  </si>
+  <si>
+    <t>0.0004,0.0378,0.0011,0.9944</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9831,0.0013,0.0167,0.0000</t>
-  </si>
-  <si>
-    <t>0.9344,0.0536,0.0082,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0029,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.9680,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0170,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0012,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.0006,0.9993</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.8470,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.8298,0.9073,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.5419,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.8007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9971,0.8884,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0023,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0020,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9882,0.0201,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0017,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0022,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0024,0.0000,0.0000</t>
+    <t>0.0000,1.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.5671,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0056,0.0000</t>
+  </si>
+  <si>
+    <t>0.6613,0.3436,0.0096,0.0002</t>
+  </si>
+  <si>
+    <t>0.6099,0.3624,0.0100,0.0008</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9511,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9851,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0033,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.0015,0.9960,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9149,0.0013,0.0962,0.0003</t>
+  </si>
+  <si>
+    <t>0.1709,0.0002,0.8812,0.0001</t>
+  </si>
+  <si>
+    <t>0.9265,0.0022,0.0562,0.0006</t>
+  </si>
+  <si>
+    <t>0.0543,0.0000,0.0000,0.9889</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9945,0.9915,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0031,0.9940,0.0017,0.0009</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.1550,0.8601,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.0000,0.0010,0.9983</t>
+  </si>
+  <si>
+    <t>0.9962,0.0012,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.1242,0.0099,0.9055,0.0008</t>
+  </si>
+  <si>
+    <t>0.9959,0.0001,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9973,0.0008,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.1049,0.9003,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9865,0.0110,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.0144,0.9804,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.1453,0.7505,0.0204,0.0013</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0021,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0796,0.9270,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.8200,0.1383,0.0109,0.0002</t>
+  </si>
+  <si>
+    <t>0.9768,0.0202,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.0336,0.2918,0.8390,0.0005</t>
+  </si>
+  <si>
+    <t>0.9917,0.0111,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0559,0.9516,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0032,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9834,0.0099,0.0039,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.0022,0.9977,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0036,0.0011,0.9971,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0033,0.0035,0.9900,0.0006</t>
+  </si>
+  <si>
+    <t>0.0028,0.0007,0.9961,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.5135,0.4884,0.0010</t>
+  </si>
+  <si>
+    <t>0.0158,0.0340,0.9367,0.0018</t>
+  </si>
+  <si>
+    <t>0.0145,0.8470,0.1064,0.0003</t>
+  </si>
+  <si>
+    <t>0.0981,0.0193,0.8248,0.0008</t>
+  </si>
+  <si>
+    <t>0.8834,0.0125,0.0382,0.0030</t>
+  </si>
+  <si>
+    <t>0.0278,0.0064,0.9456,0.0031</t>
+  </si>
+  <si>
+    <t>0.0348,0.9698,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0237,0.9709,0.0029,0.0000</t>
+  </si>
+  <si>
+    <t>0.0047,0.9956,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0071,0.9931,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7135,0.2574,0.0045,0.0002</t>
+  </si>
+  <si>
+    <t>0.9904,0.0004,0.0055,0.0000</t>
+  </si>
+  <si>
+    <t>0.9716,0.0064,0.0058,0.0017</t>
+  </si>
+  <si>
+    <t>0.9527,0.0019,0.0266,0.0013</t>
+  </si>
+  <si>
+    <t>0.9612,0.0007,0.0289,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.0023,0.9972,0.0042</t>
+  </si>
+  <si>
+    <t>0.0032,0.8006,0.7982,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9983,0.0008</t>
+  </si>
+  <si>
+    <t>0.9969,0.0020,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9949,0.0035,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0010,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0017,0.0169,0.9942,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9992,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9977,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9986,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0609,0.9445,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.7446,0.0009,0.2220,0.0012</t>
-  </si>
-  <si>
-    <t>0.9946,0.0003,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.5279,0.0416,0.2129,0.0017</t>
-  </si>
-  <si>
-    <t>0.6478,0.0012,0.4065,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.1377,0.0021,0.9803</t>
-  </si>
-  <si>
-    <t>0.0004,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.9463,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9747,0.0206,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.1597,0.8305,0.0038,0.0007</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0005,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9589,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0485,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0024,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0032,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.5992,0.0104,0.3624,0.0027</t>
-  </si>
-  <si>
-    <t>0.1493,0.0001,0.8846,0.0002</t>
-  </si>
-  <si>
-    <t>0.9643,0.0033,0.0109,0.0006</t>
-  </si>
-  <si>
-    <t>0.1611,0.0001,0.0001,0.9556</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9965,0.9449,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.9980,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9981,0.0001,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.5988,0.4301,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0639,0.0000,0.0009,0.9775</t>
-  </si>
-  <si>
-    <t>0.0127,0.0158,0.9880,0.0009</t>
-  </si>
-  <si>
-    <t>0.9855,0.0003,0.0029,0.0038</t>
-  </si>
-  <si>
-    <t>0.9886,0.0045,0.0014,0.0019</t>
-  </si>
-  <si>
-    <t>0.7230,0.3622,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0006,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9937,0.0054,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.7230,0.1276,0.0220,0.0005</t>
-  </si>
-  <si>
-    <t>0.7639,0.0152,0.1626,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0008,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0007,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9966,0.0013,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9946,0.0028,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.1647,0.8549,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.2845,0.7149,0.0049,0.0001</t>
-  </si>
-  <si>
-    <t>0.8577,0.1432,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.0085,0.7279,0.8771,0.0005</t>
-  </si>
-  <si>
-    <t>0.9903,0.0142,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0016,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9044,0.1603,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0009,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.9856,0.0067,0.0030,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.9980,0.0013</t>
-  </si>
-  <si>
-    <t>0.0012,0.0002,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0060,0.0009,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0061,0.0016,0.9871,0.0004</t>
-  </si>
-  <si>
-    <t>0.0057,0.0008,0.9925,0.0002</t>
-  </si>
-  <si>
-    <t>0.0044,0.0152,0.9711,0.0017</t>
-  </si>
-  <si>
-    <t>0.0024,0.0182,0.9891,0.0001</t>
-  </si>
-  <si>
-    <t>0.0422,0.2323,0.5043,0.0010</t>
-  </si>
-  <si>
-    <t>0.3751,0.0034,0.6310,0.0002</t>
-  </si>
-  <si>
-    <t>0.9579,0.0011,0.0268,0.0011</t>
-  </si>
-  <si>
-    <t>0.3997,0.0029,0.5927,0.0009</t>
-  </si>
-  <si>
-    <t>0.0052,0.9947,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9989,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0421,0.9622,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0117,0.9910,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0058,0.9945,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.1270,0.8882,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0001,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.8453,0.0004,0.1209,0.0039</t>
-  </si>
-  <si>
-    <t>0.8881,0.0026,0.0901,0.0020</t>
-  </si>
-  <si>
-    <t>0.9089,0.0021,0.0645,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0016</t>
-  </si>
-  <si>
-    <t>0.0021,0.0035,0.9933,0.0011</t>
-  </si>
-  <si>
-    <t>0.0035,0.5499,0.8569,0.0009</t>
-  </si>
-  <si>
-    <t>0.0008,0.0005,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0011,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9688,0.0318,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9724,0.0494,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0011,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0036,0.9989,0.0031</t>
-  </si>
-  <si>
-    <t>0.0310,0.5277,0.2019,0.0023</t>
-  </si>
-  <si>
-    <t>0.9950,0.0002,0.0025,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.0010,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0425,0.9929,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0012,0.9979,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0012,0.9964,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.0607,0.9987,0.0006</t>
-  </si>
-  <si>
-    <t>0.9896,0.0003,0.0061,0.0001</t>
-  </si>
-  <si>
-    <t>0.4662,0.0009,0.5728,0.0007</t>
-  </si>
-  <si>
-    <t>0.9976,0.0000,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0048,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9943,0.0044,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9941,0.0082,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0013,0.9925,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0396,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.0264,0.9691,0.0013</t>
-  </si>
-  <si>
-    <t>0.0092,0.0151,0.9540,0.0006</t>
-  </si>
-  <si>
-    <t>0.0030,0.0011,0.9785,0.0219</t>
-  </si>
-  <si>
-    <t>0.4904,0.0021,0.4932,0.0004</t>
-  </si>
-  <si>
-    <t>0.0281,0.0002,0.9544,0.0020</t>
-  </si>
-  <si>
-    <t>0.9838,0.0000,0.0001,0.0197</t>
-  </si>
-  <si>
-    <t>0.0016,0.0350,0.0003,0.9961</t>
-  </si>
-  <si>
-    <t>0.2960,0.0001,0.0008,0.8869</t>
-  </si>
-  <si>
-    <t>0.8403,0.0299,0.0085,0.0283</t>
+    <t>0.0006,0.0195,0.9977,0.0014</t>
+  </si>
+  <si>
+    <t>0.0563,0.3317,0.3571,0.0014</t>
+  </si>
+  <si>
+    <t>0.9473,0.0002,0.0427,0.0009</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.7138,0.8700,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0176,0.0018,0.9836,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0011,0.9954,0.0007</t>
+  </si>
+  <si>
+    <t>0.0003,0.0709,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.9710,0.0004,0.0279,0.0001</t>
+  </si>
+  <si>
+    <t>0.7158,0.0001,0.3385,0.0003</t>
+  </si>
+  <si>
+    <t>0.9954,0.0002,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0018,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9952,0.0044,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0013,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0024,0.9935,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0114,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.0083,0.9747,0.0025</t>
+  </si>
+  <si>
+    <t>0.0351,0.0100,0.9183,0.0008</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0595,0.0080,0.8723,0.0253</t>
+  </si>
+  <si>
+    <t>0.0239,0.0064,0.9571,0.0030</t>
+  </si>
+  <si>
+    <t>0.0031,0.0004,0.9937,0.0029</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.0025,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0059,0.0001,0.0021,0.9971</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.6531,0.0124,0.0087,0.1783</t>
   </si>
 </sst>
 </file>
@@ -1872,7 +1893,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1886,7 +1907,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1900,7 +1921,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1914,7 +1935,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1928,7 +1949,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1942,7 +1963,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1956,7 +1977,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1970,7 +1991,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1984,7 +2005,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1998,7 +2019,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2012,7 +2033,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2026,7 +2047,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2040,7 +2061,7 @@
         <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2054,7 +2075,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2068,7 +2089,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2082,7 +2103,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2096,7 +2117,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2110,7 +2131,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2124,7 +2145,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2135,10 +2156,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2152,7 +2173,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2166,7 +2187,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2180,7 +2201,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2191,10 +2212,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2208,7 +2229,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2222,7 +2243,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2236,7 +2257,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2250,7 +2271,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2264,7 +2285,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2278,7 +2299,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2292,7 +2313,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2306,7 +2327,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2317,10 +2338,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2334,7 +2355,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2345,10 +2366,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2362,7 +2383,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2376,7 +2397,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2387,10 +2408,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2404,7 +2425,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2418,7 +2439,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2432,7 +2453,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2446,7 +2467,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2460,7 +2481,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2474,7 +2495,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2485,10 +2506,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2502,7 +2523,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2516,7 +2537,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2530,7 +2551,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2544,7 +2565,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2558,7 +2579,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2572,7 +2593,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2586,7 +2607,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2600,7 +2621,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2614,7 +2635,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2628,7 +2649,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>274</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2642,7 +2663,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2656,7 +2677,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2670,7 +2691,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2684,7 +2705,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2698,7 +2719,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2712,7 +2733,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2726,7 +2747,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2740,7 +2761,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2754,7 +2775,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2768,7 +2789,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2782,7 +2803,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2796,7 +2817,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2810,7 +2831,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2824,7 +2845,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2838,7 +2859,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2852,7 +2873,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2866,7 +2887,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2880,7 +2901,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2891,10 +2912,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2908,7 +2929,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2922,7 +2943,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2936,7 +2957,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2950,7 +2971,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2964,7 +2985,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2978,7 +2999,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2992,7 +3013,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3006,7 +3027,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3020,7 +3041,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3034,7 +3055,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3048,7 +3069,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3062,7 +3083,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3076,7 +3097,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3090,7 +3111,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3104,7 +3125,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3118,7 +3139,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3132,7 +3153,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3146,7 +3167,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3160,7 +3181,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3174,7 +3195,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3188,7 +3209,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3202,7 +3223,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>270</v>
+        <v>358</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3216,7 +3237,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3230,7 +3251,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>270</v>
+        <v>358</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3244,7 +3265,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>358</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3258,7 +3279,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3272,7 +3293,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3286,7 +3307,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3300,7 +3321,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>358</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3314,7 +3335,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>326</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3328,7 +3349,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3342,7 +3363,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3356,7 +3377,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3370,7 +3391,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3384,7 +3405,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3398,7 +3419,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3412,7 +3433,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3426,7 +3447,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>364</v>
+        <v>281</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3440,7 +3461,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3454,7 +3475,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3465,10 +3486,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3479,10 +3500,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3493,10 +3514,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3507,10 +3528,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3524,7 +3545,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3538,7 +3559,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3552,7 +3573,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>280</v>
+        <v>374</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3566,7 +3587,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3580,7 +3601,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3594,7 +3615,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3608,7 +3629,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3619,10 +3640,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3636,7 +3657,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>269</v>
+        <v>358</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3650,7 +3671,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>320</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3664,7 +3685,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3678,7 +3699,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3692,7 +3713,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3706,7 +3727,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3720,7 +3741,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3734,7 +3755,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3748,7 +3769,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3759,10 +3780,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3776,7 +3797,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3790,7 +3811,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3804,7 +3825,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3818,7 +3839,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3832,7 +3853,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3846,7 +3867,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3860,7 +3881,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3874,7 +3895,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3888,7 +3909,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3902,7 +3923,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3916,7 +3937,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3930,7 +3951,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3944,7 +3965,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3958,7 +3979,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3969,10 +3990,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3986,7 +4007,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4000,7 +4021,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4014,7 +4035,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>406</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4028,7 +4049,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4042,7 +4063,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4056,7 +4077,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4067,10 +4088,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4084,7 +4105,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4098,7 +4119,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4109,10 +4130,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4123,10 +4144,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4140,7 +4161,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4154,7 +4175,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>274</v>
+        <v>416</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4168,7 +4189,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4182,7 +4203,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4196,7 +4217,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4210,7 +4231,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>320</v>
+        <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4224,7 +4245,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4238,7 +4259,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>352</v>
+        <v>386</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4252,7 +4273,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>357</v>
+        <v>422</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4266,7 +4287,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4277,10 +4298,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4294,7 +4315,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4305,10 +4326,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4322,7 +4343,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4336,7 +4357,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4350,7 +4371,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4361,10 +4382,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4378,7 +4399,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4392,7 +4413,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4406,7 +4427,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>424</v>
+        <v>360</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4420,7 +4441,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4434,7 +4455,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4448,7 +4469,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4462,7 +4483,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>326</v>
+        <v>436</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4476,7 +4497,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4490,7 +4511,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4504,7 +4525,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4518,7 +4539,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4529,10 +4550,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4546,7 +4567,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4557,10 +4578,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4574,7 +4595,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4588,7 +4609,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4602,7 +4623,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4616,7 +4637,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4630,7 +4651,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4644,7 +4665,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4658,7 +4679,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4672,7 +4693,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4683,10 +4704,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4700,7 +4721,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4714,7 +4735,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4728,7 +4749,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4742,7 +4763,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4756,7 +4777,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4770,7 +4791,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4784,7 +4805,7 @@
         <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4798,7 +4819,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4812,7 +4833,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4826,7 +4847,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>453</v>
+        <v>380</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4840,7 +4861,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4854,7 +4875,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4868,7 +4889,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4882,7 +4903,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4896,7 +4917,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4910,7 +4931,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>459</v>
+        <v>418</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4924,7 +4945,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4938,7 +4959,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4949,10 +4970,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4966,7 +4987,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4980,7 +5001,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4994,7 +5015,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5005,10 +5026,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5022,7 +5043,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5036,7 +5057,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5050,7 +5071,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5064,7 +5085,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5078,7 +5099,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5092,7 +5113,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5103,10 +5124,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5120,7 +5141,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5134,7 +5155,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>475</v>
+        <v>323</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5148,7 +5169,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5162,7 +5183,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>477</v>
+        <v>323</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5176,7 +5197,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5190,7 +5211,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>270</v>
+        <v>358</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5204,7 +5225,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5218,7 +5239,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>274</v>
+        <v>323</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5232,7 +5253,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5246,7 +5267,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5260,7 +5281,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5274,7 +5295,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5288,7 +5309,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5302,7 +5323,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>310</v>
+        <v>489</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5316,7 +5337,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5327,10 +5348,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5344,7 +5365,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5358,7 +5379,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5372,7 +5393,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5386,7 +5407,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5400,7 +5421,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5414,7 +5435,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>391</v>
+        <v>496</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5428,7 +5449,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
